--- a/Budgeting System_Approval Workflow.xlsx
+++ b/Budgeting System_Approval Workflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF1CD37-5FFC-4AD9-BB4D-7ECD6C8CE361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB15B66E-BFD9-455D-AFA4-3F744EE0D1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{218A4250-7EF3-40DE-92B7-3B5157644AF1}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="74">
   <si>
     <t>Module 1 - Annual Budget Setting</t>
   </si>
@@ -132,9 +132,6 @@
     <t>Centralized Department Head</t>
   </si>
   <si>
-    <t>SBU Finance Validation</t>
-  </si>
-  <si>
     <t>SBU Finance Head</t>
   </si>
   <si>
@@ -241,6 +238,30 @@
   </si>
   <si>
     <t>Refer to file 'Budegting System_User Management', tab 'User List'</t>
+  </si>
+  <si>
+    <t>SBU Finance Reviewer</t>
+  </si>
+  <si>
+    <t>Budget Officer</t>
+  </si>
+  <si>
+    <t>Create Request</t>
+  </si>
+  <si>
+    <t>Department Approval</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Endorsement</t>
+  </si>
+  <si>
+    <t>Approval</t>
+  </si>
+  <si>
+    <t>Implementation</t>
   </si>
 </sst>
 </file>
@@ -291,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -317,6 +338,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,26 +676,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA29CCB3-181B-48AA-B0D6-298770AB62E7}">
-  <dimension ref="A3:S42"/>
+  <dimension ref="A2:T42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" customWidth="1"/>
     <col min="4" max="5" width="10.81640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="13.7265625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" style="5" customWidth="1"/>
-    <col min="8" max="9" width="11.54296875" style="5" customWidth="1"/>
-    <col min="10" max="11" width="13.54296875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" style="5" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.54296875" style="5" customWidth="1"/>
-    <col min="18" max="18" width="12.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.26953125" customWidth="1"/>
+    <col min="8" max="10" width="11.54296875" style="5" customWidth="1"/>
+    <col min="11" max="12" width="13.54296875" style="5" customWidth="1"/>
+    <col min="13" max="13" width="10.81640625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="11.54296875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B3" s="6" t="s">
         <v>24</v>
       </c>
@@ -679,399 +753,420 @@
         <v>28</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="J3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="L3" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="5"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="5"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1092,624 +1187,658 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S12" s="4"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1727,8 +1856,9 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S24" s="4"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1749,8 +1879,9 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S25" s="4"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1771,232 +1902,233 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S26" s="4"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R30" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -2014,8 +2146,9 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S31" s="4"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2036,344 +2169,345 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S32" s="4"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S33" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S34" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R35" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>21</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R37" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S37" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>10</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R38" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -2391,64 +2525,65 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S39" s="4"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -2466,61 +2601,62 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S41" s="4"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R42" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="S42" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2541,48 +2677,48 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2590,10 +2726,10 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" t="str">
         <f>A12</f>
@@ -2603,24 +2739,24 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -2628,43 +2764,43 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -2673,45 +2809,45 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -2719,10 +2855,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -2730,43 +2866,43 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
